--- a/data/nzd0476/nzd0476.xlsx
+++ b/data/nzd0476/nzd0476.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O620"/>
+  <dimension ref="A1:O625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32046,6 +32046,261 @@
         <v>319.44</v>
       </c>
       <c r="O620" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>319.81</v>
+      </c>
+      <c r="C621" t="n">
+        <v>311.03</v>
+      </c>
+      <c r="D621" t="n">
+        <v>310</v>
+      </c>
+      <c r="E621" t="n">
+        <v>309.13</v>
+      </c>
+      <c r="F621" t="n">
+        <v>310.86</v>
+      </c>
+      <c r="G621" t="n">
+        <v>316.46</v>
+      </c>
+      <c r="H621" t="n">
+        <v>315.54</v>
+      </c>
+      <c r="I621" t="n">
+        <v>313.14</v>
+      </c>
+      <c r="J621" t="n">
+        <v>314.86</v>
+      </c>
+      <c r="K621" t="n">
+        <v>325.38</v>
+      </c>
+      <c r="L621" t="n">
+        <v>332.64</v>
+      </c>
+      <c r="M621" t="n">
+        <v>345.86</v>
+      </c>
+      <c r="N621" t="n">
+        <v>319.43</v>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>322.03</v>
+      </c>
+      <c r="C622" t="n">
+        <v>311.23</v>
+      </c>
+      <c r="D622" t="n">
+        <v>310.69</v>
+      </c>
+      <c r="E622" t="n">
+        <v>310.05</v>
+      </c>
+      <c r="F622" t="n">
+        <v>311.42</v>
+      </c>
+      <c r="G622" t="n">
+        <v>316.43</v>
+      </c>
+      <c r="H622" t="n">
+        <v>316</v>
+      </c>
+      <c r="I622" t="n">
+        <v>313.27</v>
+      </c>
+      <c r="J622" t="n">
+        <v>315.41</v>
+      </c>
+      <c r="K622" t="n">
+        <v>325.73</v>
+      </c>
+      <c r="L622" t="n">
+        <v>332.91</v>
+      </c>
+      <c r="M622" t="n">
+        <v>345.24</v>
+      </c>
+      <c r="N622" t="n">
+        <v>317.05</v>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:44+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>322.03</v>
+      </c>
+      <c r="C623" t="n">
+        <v>311.23</v>
+      </c>
+      <c r="D623" t="n">
+        <v>312.48</v>
+      </c>
+      <c r="E623" t="n">
+        <v>311.78</v>
+      </c>
+      <c r="F623" t="n">
+        <v>313.69</v>
+      </c>
+      <c r="G623" t="n">
+        <v>319.03</v>
+      </c>
+      <c r="H623" t="n">
+        <v>317.66</v>
+      </c>
+      <c r="I623" t="n">
+        <v>313.27</v>
+      </c>
+      <c r="J623" t="n">
+        <v>315.41</v>
+      </c>
+      <c r="K623" t="n">
+        <v>325.73</v>
+      </c>
+      <c r="L623" t="n">
+        <v>332.68</v>
+      </c>
+      <c r="M623" t="n">
+        <v>345.24</v>
+      </c>
+      <c r="N623" t="n">
+        <v>317.05</v>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>324.26</v>
+      </c>
+      <c r="C624" t="n">
+        <v>311.6</v>
+      </c>
+      <c r="D624" t="n">
+        <v>312.75</v>
+      </c>
+      <c r="E624" t="n">
+        <v>311.9</v>
+      </c>
+      <c r="F624" t="n">
+        <v>313.65</v>
+      </c>
+      <c r="G624" t="n">
+        <v>318.91</v>
+      </c>
+      <c r="H624" t="n">
+        <v>317.91</v>
+      </c>
+      <c r="I624" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="J624" t="n">
+        <v>315.41</v>
+      </c>
+      <c r="K624" t="n">
+        <v>325.81</v>
+      </c>
+      <c r="L624" t="n">
+        <v>332.77</v>
+      </c>
+      <c r="M624" t="n">
+        <v>345.08</v>
+      </c>
+      <c r="N624" t="n">
+        <v>315.38</v>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>325.74</v>
+      </c>
+      <c r="C625" t="n">
+        <v>311.63</v>
+      </c>
+      <c r="D625" t="n">
+        <v>312.52</v>
+      </c>
+      <c r="E625" t="n">
+        <v>311.67</v>
+      </c>
+      <c r="F625" t="n">
+        <v>313.39</v>
+      </c>
+      <c r="G625" t="n">
+        <v>318.38</v>
+      </c>
+      <c r="H625" t="n">
+        <v>317.79</v>
+      </c>
+      <c r="I625" t="n">
+        <v>313.59</v>
+      </c>
+      <c r="J625" t="n">
+        <v>315.26</v>
+      </c>
+      <c r="K625" t="n">
+        <v>325.72</v>
+      </c>
+      <c r="L625" t="n">
+        <v>332.57</v>
+      </c>
+      <c r="M625" t="n">
+        <v>344.28</v>
+      </c>
+      <c r="N625" t="n">
+        <v>313.22</v>
+      </c>
+      <c r="O625" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32062,7 +32317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B695"/>
+  <dimension ref="A1:B700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39015,6 +39270,56 @@
       </c>
       <c r="B695" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -39183,28 +39488,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2590400877241909</v>
+        <v>0.2541099012198552</v>
       </c>
       <c r="J2" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K2" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02293714368301969</v>
+        <v>0.02242921486216976</v>
       </c>
       <c r="M2" t="n">
-        <v>8.845221216365472</v>
+        <v>8.79954279440109</v>
       </c>
       <c r="N2" t="n">
-        <v>123.0425594277235</v>
+        <v>122.1542061854686</v>
       </c>
       <c r="O2" t="n">
-        <v>11.09245506764501</v>
+        <v>11.05233939876389</v>
       </c>
       <c r="P2" t="n">
-        <v>318.8285951802981</v>
+        <v>318.8893071270066</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -39265,28 +39570,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05405082461784013</v>
+        <v>-0.0483832477139633</v>
       </c>
       <c r="J3" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K3" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007228880214391609</v>
+        <v>0.005866583666666481</v>
       </c>
       <c r="M3" t="n">
-        <v>3.378005904276449</v>
+        <v>3.371188522094326</v>
       </c>
       <c r="N3" t="n">
-        <v>17.27113924265506</v>
+        <v>17.21791444593519</v>
       </c>
       <c r="O3" t="n">
-        <v>4.155856018037086</v>
+        <v>4.149447486827034</v>
       </c>
       <c r="P3" t="n">
-        <v>309.4766658220831</v>
+        <v>309.4068397246635</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39343,28 +39648,28 @@
         <v>0.1631</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1686705961754551</v>
+        <v>-0.1644203499597255</v>
       </c>
       <c r="J4" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K4" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09303529118741449</v>
+        <v>0.08974856275026277</v>
       </c>
       <c r="M4" t="n">
-        <v>2.732136521135415</v>
+        <v>2.729502963037378</v>
       </c>
       <c r="N4" t="n">
-        <v>11.93877199048862</v>
+        <v>11.90079887522819</v>
       </c>
       <c r="O4" t="n">
-        <v>3.455252811371206</v>
+        <v>3.449753451368401</v>
       </c>
       <c r="P4" t="n">
-        <v>313.6557546804687</v>
+        <v>313.6033789859757</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39421,28 +39726,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1975784070211321</v>
+        <v>-0.1929317267461235</v>
       </c>
       <c r="J5" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K5" t="n">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09974844650800896</v>
+        <v>0.09658389919542076</v>
       </c>
       <c r="M5" t="n">
-        <v>3.117398778139394</v>
+        <v>3.113850733512761</v>
       </c>
       <c r="N5" t="n">
-        <v>15.17184512552124</v>
+        <v>15.11693480463089</v>
       </c>
       <c r="O5" t="n">
-        <v>3.895105277848244</v>
+        <v>3.88805025747236</v>
       </c>
       <c r="P5" t="n">
-        <v>313.4054870646327</v>
+        <v>313.3481882739154</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39499,28 +39804,28 @@
         <v>0.142</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1919534404619499</v>
+        <v>-0.1845717982540983</v>
       </c>
       <c r="J6" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K6" t="n">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07560496909417258</v>
+        <v>0.07084291198696191</v>
       </c>
       <c r="M6" t="n">
-        <v>3.486087505391581</v>
+        <v>3.488041982074206</v>
       </c>
       <c r="N6" t="n">
-        <v>19.39995693865838</v>
+        <v>19.39977854246024</v>
       </c>
       <c r="O6" t="n">
-        <v>4.404538220819338</v>
+        <v>4.40451796936512</v>
       </c>
       <c r="P6" t="n">
-        <v>313.3675245163615</v>
+        <v>313.2765073527053</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39577,28 +39882,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1844659390761811</v>
+        <v>-0.1753600763962838</v>
       </c>
       <c r="J7" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K7" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07904025147450022</v>
+        <v>0.07216814098916935</v>
       </c>
       <c r="M7" t="n">
-        <v>3.288317948209434</v>
+        <v>3.298748766811261</v>
       </c>
       <c r="N7" t="n">
-        <v>17.06722606892412</v>
+        <v>17.15996204113479</v>
       </c>
       <c r="O7" t="n">
-        <v>4.131249940263131</v>
+        <v>4.142458453760858</v>
       </c>
       <c r="P7" t="n">
-        <v>317.405871463834</v>
+        <v>317.2936767460185</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39655,28 +39960,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2096390766930412</v>
+        <v>-0.2037605421909755</v>
       </c>
       <c r="J8" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K8" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="L8" t="n">
-        <v>0.142675717032309</v>
+        <v>0.1367486807388008</v>
       </c>
       <c r="M8" t="n">
-        <v>2.736289034649771</v>
+        <v>2.741974460633803</v>
       </c>
       <c r="N8" t="n">
-        <v>11.36783518929384</v>
+        <v>11.3758901292686</v>
       </c>
       <c r="O8" t="n">
-        <v>3.371622041287226</v>
+        <v>3.372816349768928</v>
       </c>
       <c r="P8" t="n">
-        <v>319.0808503906432</v>
+        <v>319.0084157294717</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39733,28 +40038,28 @@
         <v>0.0941</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1835223969164885</v>
+        <v>-0.1819617982057858</v>
       </c>
       <c r="J9" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K9" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09600383973840865</v>
+        <v>0.09589479289774505</v>
       </c>
       <c r="M9" t="n">
-        <v>2.937290794726295</v>
+        <v>2.919626749352313</v>
       </c>
       <c r="N9" t="n">
-        <v>13.65193962365454</v>
+        <v>13.54925739866337</v>
       </c>
       <c r="O9" t="n">
-        <v>3.694853126127552</v>
+        <v>3.680931593858186</v>
       </c>
       <c r="P9" t="n">
-        <v>317.2953303462889</v>
+        <v>317.2761018366061</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39811,28 +40116,28 @@
         <v>0.0854</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2246086900210104</v>
+        <v>-0.2228688218059772</v>
       </c>
       <c r="J10" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K10" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09208237389490959</v>
+        <v>0.09211347298657491</v>
       </c>
       <c r="M10" t="n">
-        <v>3.657553470413248</v>
+        <v>3.636562153673149</v>
       </c>
       <c r="N10" t="n">
-        <v>21.41219951021982</v>
+        <v>21.24898338208897</v>
       </c>
       <c r="O10" t="n">
-        <v>4.627331791672153</v>
+        <v>4.609661959633153</v>
       </c>
       <c r="P10" t="n">
-        <v>320.16687071608</v>
+        <v>320.1454347782018</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39889,28 +40194,28 @@
         <v>0.1648</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2552384710454156</v>
+        <v>-0.2482433185022936</v>
       </c>
       <c r="J11" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K11" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08275719481198696</v>
+        <v>0.07951865526666102</v>
       </c>
       <c r="M11" t="n">
-        <v>4.373023415515127</v>
+        <v>4.368049330099921</v>
       </c>
       <c r="N11" t="n">
-        <v>31.08200689401809</v>
+        <v>30.96222831033167</v>
       </c>
       <c r="O11" t="n">
-        <v>5.575123935305662</v>
+        <v>5.564371331096773</v>
       </c>
       <c r="P11" t="n">
-        <v>328.3244864933625</v>
+        <v>328.2383066675464</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39967,28 +40272,28 @@
         <v>0.0694</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2098101486936434</v>
+        <v>-0.2066093833552075</v>
       </c>
       <c r="J12" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K12" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0345261942527002</v>
+        <v>0.03403250422536541</v>
       </c>
       <c r="M12" t="n">
-        <v>5.508936142315869</v>
+        <v>5.477386219485632</v>
       </c>
       <c r="N12" t="n">
-        <v>52.73937508227856</v>
+        <v>52.34306962943302</v>
       </c>
       <c r="O12" t="n">
-        <v>7.262188036830123</v>
+        <v>7.234851044039057</v>
       </c>
       <c r="P12" t="n">
-        <v>336.3815162468586</v>
+        <v>336.3419810546611</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -40049,28 +40354,28 @@
         <v>0.0512</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0570620998604974</v>
+        <v>0.06332710332519613</v>
       </c>
       <c r="J13" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K13" t="n">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001311137793311379</v>
+        <v>0.001639272118957202</v>
       </c>
       <c r="M13" t="n">
-        <v>7.489389493996855</v>
+        <v>7.452879615955031</v>
       </c>
       <c r="N13" t="n">
-        <v>106.3701426898102</v>
+        <v>105.6202427796197</v>
       </c>
       <c r="O13" t="n">
-        <v>10.3135901940018</v>
+        <v>10.27717095214533</v>
       </c>
       <c r="P13" t="n">
-        <v>340.0167040993928</v>
+        <v>339.9393344777008</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -40131,28 +40436,28 @@
         <v>0.0428</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5520329600769452</v>
+        <v>0.5319446475842514</v>
       </c>
       <c r="J14" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="K14" t="n">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03047171022299944</v>
+        <v>0.0287421226564899</v>
       </c>
       <c r="M14" t="n">
-        <v>13.52357780550783</v>
+        <v>13.48412034610872</v>
       </c>
       <c r="N14" t="n">
-        <v>405.0082241860273</v>
+        <v>402.7848063799107</v>
       </c>
       <c r="O14" t="n">
-        <v>20.12481612800542</v>
+        <v>20.06949940531429</v>
       </c>
       <c r="P14" t="n">
-        <v>313.27001341603</v>
+        <v>313.5215350287798</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -40194,7 +40499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O620"/>
+  <dimension ref="A1:O625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87885,6 +88190,391 @@
         </is>
       </c>
     </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>-45.18291142030344,170.90580681239547</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>-45.18291642630122,170.9048621193442</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>-45.18315643835809,170.90393186753832</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>-45.183541005753476,170.90312765180138</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>-45.184011585820244,170.90246481806656</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>-45.18452663688477,170.90189141202245</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>-45.18505119045171,170.90133254810485</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>-45.18560614478692,170.90084674596963</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>-45.186184750918656,170.90045617569032</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>-45.186790598814554,170.90018545811395</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>-45.1873610716665,170.89980088739526</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>-45.18795853725383,170.89949181996315</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>-45.18855549671948,170.8991176804124</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>-45.18293128585599,170.90580979180723</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>-45.182918180173665,170.90486269014298</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>-45.18316197710098,170.9039358355601</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>-45.1835474888207,170.90313493199082</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>-45.18401516702366,170.90246983121324</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>-45.184526462094716,170.901891121104</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>-45.185053502478524,170.90133740330572</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>-45.18560671689096,170.9008481888735</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>-45.18618702972843,170.9004623883948</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>-45.18679215765,170.9001893281058</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>-45.187362360575726,170.89980379987833</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>-45.187956822181484,170.8994843123022</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>-45.188554066341005,170.89908746146654</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:44+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>-45.18293128585599,170.90580979180723</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>-45.182918180173665,170.90486269014298</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>-45.18317634572323,170.90394612941725</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>-45.183559679804624,170.90314862191673</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>-45.18402968368535,170.90249015236776</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>-45.184541610563116,170.90191633404308</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>-45.18506184587794,170.90135492425125</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>-45.18560671689096,170.9008481888735</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>-45.18618702972843,170.9004623883948</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>-45.18679215765,170.9001893281058</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>-45.18736126261602,170.89980131887424</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>-45.187956822181484,170.8994843123022</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>-45.188554066341005,170.89908746146654</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>-45.18295124089291,170.90581278464157</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>-45.18292142483769,170.90486374612084</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>-45.183178513057236,170.90394768212238</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>-45.18356052542194,170.90314957150719</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>-45.18402942788517,170.90248979428566</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>-45.184540911403154,170.90191517036865</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>-45.185063102413764,170.9013575629483</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>-45.18560816915503,170.9008518516296</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>-45.18618702972843,170.9004623883948</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>-45.186792513955226,170.90019021267543</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>-45.18736169225244,170.8998022897019</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>-45.187956379582104,170.8994823748414</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>-45.188553062667296,170.89906625741736</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>-45.18296448459448,170.9058147709183</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>-45.182921687918544,170.90486383174064</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>-45.18317666680976,170.90394635944762</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>-45.1835589046554,170.90314775145885</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>-45.18402776518399,170.902487466752</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>-45.18453782344651,170.90191003080704</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>-45.185062499276576,170.9013562963737</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>-45.185608125147034,170.900851740637</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>-45.18618640823489,170.90046069402078</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>-45.186792113111835,170.9001892175346</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>-45.18736073750484,170.89980013230712</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>-45.18795416658465,170.89947268753778</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>-45.188551764496694,170.8990388318221</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0476/nzd0476.xlsx
+++ b/data/nzd0476/nzd0476.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O625"/>
+  <dimension ref="A1:O626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32303,6 +32303,57 @@
       <c r="O625" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>326.82</v>
+      </c>
+      <c r="C626" t="n">
+        <v>311.67</v>
+      </c>
+      <c r="D626" t="n">
+        <v>312.62</v>
+      </c>
+      <c r="E626" t="n">
+        <v>310.88</v>
+      </c>
+      <c r="F626" t="n">
+        <v>312.61</v>
+      </c>
+      <c r="G626" t="n">
+        <v>317.35</v>
+      </c>
+      <c r="H626" t="n">
+        <v>317.18</v>
+      </c>
+      <c r="I626" t="n">
+        <v>313.19</v>
+      </c>
+      <c r="J626" t="n">
+        <v>315.33</v>
+      </c>
+      <c r="K626" t="n">
+        <v>324.81</v>
+      </c>
+      <c r="L626" t="n">
+        <v>331.53</v>
+      </c>
+      <c r="M626" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="N626" t="n">
+        <v>310.65</v>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -32317,7 +32368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B700"/>
+  <dimension ref="A1:B702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39320,6 +39371,26 @@
       </c>
       <c r="B700" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -39488,28 +39559,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2541099012198552</v>
+        <v>0.2545345608755979</v>
       </c>
       <c r="J2" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K2" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02242921486216976</v>
+        <v>0.02257367318909076</v>
       </c>
       <c r="M2" t="n">
-        <v>8.79954279440109</v>
+        <v>8.78725354618928</v>
       </c>
       <c r="N2" t="n">
-        <v>122.1542061854686</v>
+        <v>121.9611694111337</v>
       </c>
       <c r="O2" t="n">
-        <v>11.05233939876389</v>
+        <v>11.0436030991309</v>
       </c>
       <c r="P2" t="n">
-        <v>318.8893071270066</v>
+        <v>318.8840610218479</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -39570,28 +39641,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0483832477139633</v>
+        <v>-0.04716168197003606</v>
       </c>
       <c r="J3" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K3" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005866583666666481</v>
+        <v>0.005587311207328582</v>
       </c>
       <c r="M3" t="n">
-        <v>3.371188522094326</v>
+        <v>3.370156596946583</v>
       </c>
       <c r="N3" t="n">
-        <v>17.21791444593519</v>
+        <v>17.2103074157876</v>
       </c>
       <c r="O3" t="n">
-        <v>4.149447486827034</v>
+        <v>4.14853075386788</v>
       </c>
       <c r="P3" t="n">
-        <v>309.4068397246635</v>
+        <v>309.3917489048405</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39648,28 +39719,28 @@
         <v>0.1631</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1644203499597255</v>
+        <v>-0.1632635091696364</v>
       </c>
       <c r="J4" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K4" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08974856275026277</v>
+        <v>0.08874251426047552</v>
       </c>
       <c r="M4" t="n">
-        <v>2.729502963037378</v>
+        <v>2.730426567835218</v>
       </c>
       <c r="N4" t="n">
-        <v>11.90079887522819</v>
+        <v>11.89964199043648</v>
       </c>
       <c r="O4" t="n">
-        <v>3.449753451368401</v>
+        <v>3.449585770847926</v>
       </c>
       <c r="P4" t="n">
-        <v>313.6033789859757</v>
+        <v>313.5890877568593</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39726,28 +39797,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1929317267461235</v>
+        <v>-0.1920270015223314</v>
       </c>
       <c r="J5" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K5" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09658389919542076</v>
+        <v>0.09598498182218751</v>
       </c>
       <c r="M5" t="n">
-        <v>3.113850733512761</v>
+        <v>3.113029634241096</v>
       </c>
       <c r="N5" t="n">
-        <v>15.11693480463089</v>
+        <v>15.10362736945409</v>
       </c>
       <c r="O5" t="n">
-        <v>3.88805025747236</v>
+        <v>3.886338555691474</v>
       </c>
       <c r="P5" t="n">
-        <v>313.3481882739154</v>
+        <v>313.3370037734069</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39804,28 +39875,28 @@
         <v>0.142</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1845717982540983</v>
+        <v>-0.1831221496923603</v>
       </c>
       <c r="J6" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K6" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07084291198696191</v>
+        <v>0.06992831213560791</v>
       </c>
       <c r="M6" t="n">
-        <v>3.488041982074206</v>
+        <v>3.488337736057619</v>
       </c>
       <c r="N6" t="n">
-        <v>19.39977854246024</v>
+        <v>19.39677094719817</v>
       </c>
       <c r="O6" t="n">
-        <v>4.40451796936512</v>
+        <v>4.404176534517908</v>
       </c>
       <c r="P6" t="n">
-        <v>313.2765073527053</v>
+        <v>313.2585863368549</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39882,28 +39953,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1753600763962838</v>
+        <v>-0.1737439050437395</v>
       </c>
       <c r="J7" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K7" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07216814098916935</v>
+        <v>0.07101791555250503</v>
       </c>
       <c r="M7" t="n">
-        <v>3.298748766811261</v>
+        <v>3.300032545082467</v>
       </c>
       <c r="N7" t="n">
-        <v>17.15996204113479</v>
+        <v>17.1674122427072</v>
       </c>
       <c r="O7" t="n">
-        <v>4.142458453760858</v>
+        <v>4.143357604975366</v>
       </c>
       <c r="P7" t="n">
-        <v>317.2936767460185</v>
+        <v>317.2737110988106</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39960,28 +40031,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2037605421909755</v>
+        <v>-0.2025372982951865</v>
       </c>
       <c r="J8" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K8" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1367486807388008</v>
+        <v>0.1355075732071288</v>
       </c>
       <c r="M8" t="n">
-        <v>2.741974460633803</v>
+        <v>2.743312105220277</v>
       </c>
       <c r="N8" t="n">
-        <v>11.3758901292686</v>
+        <v>11.37768516614536</v>
       </c>
       <c r="O8" t="n">
-        <v>3.372816349768928</v>
+        <v>3.373082442832574</v>
       </c>
       <c r="P8" t="n">
-        <v>319.0084157294717</v>
+        <v>318.9933041783146</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40038,28 +40109,28 @@
         <v>0.0941</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1819617982057858</v>
+        <v>-0.1817150468578559</v>
       </c>
       <c r="J9" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K9" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09589479289774505</v>
+        <v>0.09593588507770434</v>
       </c>
       <c r="M9" t="n">
-        <v>2.919626749352313</v>
+        <v>2.915882217405679</v>
       </c>
       <c r="N9" t="n">
-        <v>13.54925739866337</v>
+        <v>13.52839225268778</v>
       </c>
       <c r="O9" t="n">
-        <v>3.680931593858186</v>
+        <v>3.678096281051896</v>
       </c>
       <c r="P9" t="n">
-        <v>317.2761018366061</v>
+        <v>317.2730535519343</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40116,28 +40187,28 @@
         <v>0.0854</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2228688218059772</v>
+        <v>-0.2225031194545746</v>
       </c>
       <c r="J10" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K10" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09211347298657491</v>
+        <v>0.09210337740428109</v>
       </c>
       <c r="M10" t="n">
-        <v>3.636562153673149</v>
+        <v>3.632482994263917</v>
       </c>
       <c r="N10" t="n">
-        <v>21.24898338208897</v>
+        <v>21.21677224726861</v>
       </c>
       <c r="O10" t="n">
-        <v>4.609661959633153</v>
+        <v>4.606166762859179</v>
       </c>
       <c r="P10" t="n">
-        <v>320.1454347782018</v>
+        <v>320.1409170121124</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40194,28 +40265,28 @@
         <v>0.1648</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2482433185022936</v>
+        <v>-0.2471684665985945</v>
       </c>
       <c r="J11" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K11" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07951865526666102</v>
+        <v>0.07908570150670802</v>
       </c>
       <c r="M11" t="n">
-        <v>4.368049330099921</v>
+        <v>4.365704464498294</v>
       </c>
       <c r="N11" t="n">
-        <v>30.96222831033167</v>
+        <v>30.92812792707067</v>
       </c>
       <c r="O11" t="n">
-        <v>5.564371331096773</v>
+        <v>5.561306314803264</v>
       </c>
       <c r="P11" t="n">
-        <v>328.2383066675464</v>
+        <v>328.2250283020586</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40272,28 +40343,28 @@
         <v>0.0694</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2066093833552075</v>
+        <v>-0.2063879351935659</v>
       </c>
       <c r="J12" t="n">
+        <v>625</v>
+      </c>
+      <c r="K12" t="n">
         <v>624</v>
       </c>
-      <c r="K12" t="n">
-        <v>623</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.03403250422536541</v>
+        <v>0.03406857618682835</v>
       </c>
       <c r="M12" t="n">
-        <v>5.477386219485632</v>
+        <v>5.46947643332541</v>
       </c>
       <c r="N12" t="n">
-        <v>52.34306962943302</v>
+        <v>52.25983758234725</v>
       </c>
       <c r="O12" t="n">
-        <v>7.234851044039057</v>
+        <v>7.229096595173372</v>
       </c>
       <c r="P12" t="n">
-        <v>336.3419810546611</v>
+        <v>336.3392382009669</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -40354,28 +40425,28 @@
         <v>0.0512</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06332710332519613</v>
+        <v>0.06363673809227273</v>
       </c>
       <c r="J13" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K13" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001639272118957202</v>
+        <v>0.00166067688683047</v>
       </c>
       <c r="M13" t="n">
-        <v>7.452879615955031</v>
+        <v>7.442076823997356</v>
       </c>
       <c r="N13" t="n">
-        <v>105.6202427796197</v>
+        <v>105.4519830400445</v>
       </c>
       <c r="O13" t="n">
-        <v>10.27717095214533</v>
+        <v>10.26898159702531</v>
       </c>
       <c r="P13" t="n">
-        <v>339.9393344777008</v>
+        <v>339.9354997891805</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -40436,28 +40507,28 @@
         <v>0.0428</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5319446475842514</v>
+        <v>0.5259555477536257</v>
       </c>
       <c r="J14" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K14" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0287421226564899</v>
+        <v>0.02817548536014158</v>
       </c>
       <c r="M14" t="n">
-        <v>13.48412034610872</v>
+        <v>13.4830261052852</v>
       </c>
       <c r="N14" t="n">
-        <v>402.7848063799107</v>
+        <v>402.5931404261011</v>
       </c>
       <c r="O14" t="n">
-        <v>20.06949940531429</v>
+        <v>20.06472378145538</v>
       </c>
       <c r="P14" t="n">
-        <v>313.5215350287798</v>
+        <v>313.5967172502282</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -40499,7 +40570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O625"/>
+  <dimension ref="A1:O626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88575,6 +88646,83 @@
         </is>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>-45.18297414891724,170.905816220364</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>-45.182922038693036,170.90486394590042</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>-45.18317746952606,170.9039469345236</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>-45.18355333767445,170.90314149998923</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>-45.184022777080216,170.902480484152</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>-45.184531822322604,170.90190004260398</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>-45.18505943332897,170.9013498579532</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>-45.18560636482694,170.90084730093267</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>-45.1861866982652,170.90046148472868</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>-45.18678806013943,170.9001791555563</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>-45.18735577281671,170.89978891385528</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>-45.18794924266241,170.89945113329009</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>-45.188550219905515,170.89900620044455</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0476/nzd0476.xlsx
+++ b/data/nzd0476/nzd0476.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O626"/>
+  <dimension ref="A1:O627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32352,6 +32352,57 @@
         <v>310.65</v>
       </c>
       <c r="O626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>331.97</v>
+      </c>
+      <c r="C627" t="n">
+        <v>313.63</v>
+      </c>
+      <c r="D627" t="n">
+        <v>314.33</v>
+      </c>
+      <c r="E627" t="n">
+        <v>311.79</v>
+      </c>
+      <c r="F627" t="n">
+        <v>313.42</v>
+      </c>
+      <c r="G627" t="n">
+        <v>318.31</v>
+      </c>
+      <c r="H627" t="n">
+        <v>318</v>
+      </c>
+      <c r="I627" t="n">
+        <v>313.14</v>
+      </c>
+      <c r="J627" t="n">
+        <v>316.27</v>
+      </c>
+      <c r="K627" t="n">
+        <v>325.6</v>
+      </c>
+      <c r="L627" t="n">
+        <v>330.37</v>
+      </c>
+      <c r="M627" t="n">
+        <v>341.67</v>
+      </c>
+      <c r="N627" t="n">
+        <v>308.29</v>
+      </c>
+      <c r="O627" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -32368,7 +32419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B702"/>
+  <dimension ref="A1:B704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39391,6 +39442,26 @@
       </c>
       <c r="B702" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -39559,28 +39630,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2545345608755979</v>
+        <v>0.2567371191755962</v>
       </c>
       <c r="J2" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K2" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02257367318909076</v>
+        <v>0.02301903648843495</v>
       </c>
       <c r="M2" t="n">
-        <v>8.78725354618928</v>
+        <v>8.782387660259527</v>
       </c>
       <c r="N2" t="n">
-        <v>121.9611694111337</v>
+        <v>121.830499647129</v>
       </c>
       <c r="O2" t="n">
-        <v>11.0436030991309</v>
+        <v>11.03768542979592</v>
       </c>
       <c r="P2" t="n">
-        <v>318.8840610218479</v>
+        <v>318.8567568604093</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -39641,28 +39712,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04716168197003606</v>
+        <v>-0.04525996710224812</v>
       </c>
       <c r="J3" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K3" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005587311207328582</v>
+        <v>0.005150673858044907</v>
       </c>
       <c r="M3" t="n">
-        <v>3.370156596946583</v>
+        <v>3.371527830027529</v>
       </c>
       <c r="N3" t="n">
-        <v>17.2103074157876</v>
+        <v>17.230642211978</v>
       </c>
       <c r="O3" t="n">
-        <v>4.14853075386788</v>
+        <v>4.150980873477738</v>
       </c>
       <c r="P3" t="n">
-        <v>309.3917489048405</v>
+        <v>309.3681741691522</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39719,28 +39790,28 @@
         <v>0.1631</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1632635091696364</v>
+        <v>-0.1615094092385318</v>
       </c>
       <c r="J4" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K4" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08874251426047552</v>
+        <v>0.08700044717369904</v>
       </c>
       <c r="M4" t="n">
-        <v>2.730426567835218</v>
+        <v>2.734013497792208</v>
       </c>
       <c r="N4" t="n">
-        <v>11.89964199043648</v>
+        <v>11.92132354302994</v>
       </c>
       <c r="O4" t="n">
-        <v>3.449585770847926</v>
+        <v>3.452726971978807</v>
       </c>
       <c r="P4" t="n">
-        <v>313.5890877568593</v>
+        <v>313.5673429396172</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39797,28 +39868,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1920270015223314</v>
+        <v>-0.1908010758764516</v>
       </c>
       <c r="J5" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K5" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09598498182218751</v>
+        <v>0.09504801975597577</v>
       </c>
       <c r="M5" t="n">
-        <v>3.113029634241096</v>
+        <v>3.113637058334417</v>
       </c>
       <c r="N5" t="n">
-        <v>15.10362736945409</v>
+        <v>15.09933130731916</v>
       </c>
       <c r="O5" t="n">
-        <v>3.886338555691474</v>
+        <v>3.885785803067271</v>
       </c>
       <c r="P5" t="n">
-        <v>313.3370037734069</v>
+        <v>313.3217956611426</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39875,28 +39946,28 @@
         <v>0.142</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1831221496923603</v>
+        <v>-0.1813867971877424</v>
       </c>
       <c r="J6" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K6" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06992831213560791</v>
+        <v>0.06877830295211618</v>
       </c>
       <c r="M6" t="n">
-        <v>3.488337736057619</v>
+        <v>3.489769910129285</v>
       </c>
       <c r="N6" t="n">
-        <v>19.39677094719817</v>
+        <v>19.40557830524416</v>
       </c>
       <c r="O6" t="n">
-        <v>4.404176534517908</v>
+        <v>4.405176308077142</v>
       </c>
       <c r="P6" t="n">
-        <v>313.2585863368549</v>
+        <v>313.2370585747129</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39953,28 +40024,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1737439050437395</v>
+        <v>-0.1717920446679935</v>
       </c>
       <c r="J7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07101791555250503</v>
+        <v>0.06956437887943001</v>
       </c>
       <c r="M7" t="n">
-        <v>3.300032545082467</v>
+        <v>3.302592447902974</v>
       </c>
       <c r="N7" t="n">
-        <v>17.1674122427072</v>
+        <v>17.19037109127717</v>
       </c>
       <c r="O7" t="n">
-        <v>4.143357604975366</v>
+        <v>4.146127240121457</v>
       </c>
       <c r="P7" t="n">
-        <v>317.2737110988106</v>
+        <v>317.2495147309755</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -40031,28 +40102,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2025372982951865</v>
+        <v>-0.2010251747334287</v>
       </c>
       <c r="J8" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K8" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1355075732071288</v>
+        <v>0.1338343142443176</v>
       </c>
       <c r="M8" t="n">
-        <v>2.743312105220277</v>
+        <v>2.745922123218074</v>
       </c>
       <c r="N8" t="n">
-        <v>11.37768516614536</v>
+        <v>11.38974840693596</v>
       </c>
       <c r="O8" t="n">
-        <v>3.373082442832574</v>
+        <v>3.374870131862255</v>
       </c>
       <c r="P8" t="n">
-        <v>318.9933041783146</v>
+        <v>318.9745590373367</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40109,28 +40180,28 @@
         <v>0.0941</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1817150468578559</v>
+        <v>-0.1814819818132174</v>
       </c>
       <c r="J9" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K9" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09593588507770434</v>
+        <v>0.09599380413707437</v>
       </c>
       <c r="M9" t="n">
-        <v>2.915882217405679</v>
+        <v>2.912092594449589</v>
       </c>
       <c r="N9" t="n">
-        <v>13.52839225268778</v>
+        <v>13.5074997578192</v>
       </c>
       <c r="O9" t="n">
-        <v>3.678096281051896</v>
+        <v>3.675255060239929</v>
       </c>
       <c r="P9" t="n">
-        <v>317.2730535519343</v>
+        <v>317.2701643455036</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40187,28 +40258,28 @@
         <v>0.0854</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2225031194545746</v>
+        <v>-0.2218043047922216</v>
       </c>
       <c r="J10" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K10" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09210337740428109</v>
+        <v>0.09182709304517722</v>
       </c>
       <c r="M10" t="n">
-        <v>3.632482994263917</v>
+        <v>3.629977688973034</v>
       </c>
       <c r="N10" t="n">
-        <v>21.21677224726861</v>
+        <v>21.18933780397804</v>
       </c>
       <c r="O10" t="n">
-        <v>4.606166762859179</v>
+        <v>4.603187787172932</v>
       </c>
       <c r="P10" t="n">
-        <v>320.1409170121124</v>
+        <v>320.1322541093612</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40265,28 +40336,28 @@
         <v>0.1648</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2471684665985945</v>
+        <v>-0.2458099716688016</v>
       </c>
       <c r="J11" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K11" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07908570150670802</v>
+        <v>0.07846702171884545</v>
       </c>
       <c r="M11" t="n">
-        <v>4.365704464498294</v>
+        <v>4.36453292598211</v>
       </c>
       <c r="N11" t="n">
-        <v>30.92812792707067</v>
+        <v>30.90312822468079</v>
       </c>
       <c r="O11" t="n">
-        <v>5.561306314803264</v>
+        <v>5.559058213823704</v>
       </c>
       <c r="P11" t="n">
-        <v>328.2250283020586</v>
+        <v>328.2081876287031</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40343,28 +40414,28 @@
         <v>0.0694</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2063879351935659</v>
+        <v>-0.2065639923284184</v>
       </c>
       <c r="J12" t="n">
+        <v>626</v>
+      </c>
+      <c r="K12" t="n">
         <v>625</v>
       </c>
-      <c r="K12" t="n">
-        <v>624</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.03406857618682835</v>
+        <v>0.03423321219668674</v>
       </c>
       <c r="M12" t="n">
-        <v>5.46947643332541</v>
+        <v>5.461653280879354</v>
       </c>
       <c r="N12" t="n">
-        <v>52.25983758234725</v>
+        <v>52.17662907442385</v>
       </c>
       <c r="O12" t="n">
-        <v>7.229096595173372</v>
+        <v>7.223339191428287</v>
       </c>
       <c r="P12" t="n">
-        <v>336.3392382009669</v>
+        <v>336.3414263925181</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -40425,28 +40496,28 @@
         <v>0.0512</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06363673809227273</v>
+        <v>0.06365303514054675</v>
       </c>
       <c r="J13" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K13" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00166067688683047</v>
+        <v>0.001666994455887472</v>
       </c>
       <c r="M13" t="n">
-        <v>7.442076823997356</v>
+        <v>7.430210796682655</v>
       </c>
       <c r="N13" t="n">
-        <v>105.4519830400445</v>
+        <v>105.2829929730919</v>
       </c>
       <c r="O13" t="n">
-        <v>10.26898159702531</v>
+        <v>10.26075011746665</v>
       </c>
       <c r="P13" t="n">
-        <v>339.9354997891805</v>
+        <v>339.9352972569205</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -40507,28 +40578,28 @@
         <v>0.0428</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5259555477536257</v>
+        <v>0.5191138203111521</v>
       </c>
       <c r="J14" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K14" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02817548536014158</v>
+        <v>0.02751692996909572</v>
       </c>
       <c r="M14" t="n">
-        <v>13.4830261052852</v>
+        <v>13.48491190593647</v>
       </c>
       <c r="N14" t="n">
-        <v>402.5931404261011</v>
+        <v>402.5365207888181</v>
       </c>
       <c r="O14" t="n">
-        <v>20.06472378145538</v>
+        <v>20.06331280693241</v>
       </c>
       <c r="P14" t="n">
-        <v>313.5967172502282</v>
+        <v>313.682895035882</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -40570,7 +40641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O626"/>
+  <dimension ref="A1:O627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88723,6 +88794,83 @@
         </is>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>-45.183020233418844,170.90582313207855</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>-45.18293922664283,170.904869539731</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>-45.18319119597435,170.9039567683252</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>-45.183559750272735,170.90314870104928</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>-45.18402795703414,170.9024877353136</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>-45.184537415603174,170.90190935199703</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>-45.18506355476665,170.90135851287928</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>-45.18560614478692,170.90084674596963</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>-45.18619059295758,170.90047210280642</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>-45.18679157865398,170.90018789068026</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>-45.18735023527871,170.89977640096905</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>-45.18794694667484,170.8994410827152</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>-45.188548801517875,170.89897623544599</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0476/nzd0476.xlsx
+++ b/data/nzd0476/nzd0476.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O627"/>
+  <dimension ref="A1:O630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32405,6 +32405,159 @@
       <c r="O627" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>332.42</v>
+      </c>
+      <c r="C628" t="n">
+        <v>313.81</v>
+      </c>
+      <c r="D628" t="n">
+        <v>314.05</v>
+      </c>
+      <c r="E628" t="n">
+        <v>311.57</v>
+      </c>
+      <c r="F628" t="n">
+        <v>312.99</v>
+      </c>
+      <c r="G628" t="n">
+        <v>317.75</v>
+      </c>
+      <c r="H628" t="n">
+        <v>317.66</v>
+      </c>
+      <c r="I628" t="n">
+        <v>312.74</v>
+      </c>
+      <c r="J628" t="n">
+        <v>315.26</v>
+      </c>
+      <c r="K628" t="n">
+        <v>324.34</v>
+      </c>
+      <c r="L628" t="n">
+        <v>329.42</v>
+      </c>
+      <c r="M628" t="n">
+        <v>341.43</v>
+      </c>
+      <c r="N628" t="n">
+        <v>305.9</v>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>329.41</v>
+      </c>
+      <c r="C629" t="n">
+        <v>312.68</v>
+      </c>
+      <c r="D629" t="n">
+        <v>312.57</v>
+      </c>
+      <c r="E629" t="n">
+        <v>309.58</v>
+      </c>
+      <c r="F629" t="n">
+        <v>311.28</v>
+      </c>
+      <c r="G629" t="n">
+        <v>316.16</v>
+      </c>
+      <c r="H629" t="n">
+        <v>315.96</v>
+      </c>
+      <c r="I629" t="n">
+        <v>311.26</v>
+      </c>
+      <c r="J629" t="n">
+        <v>313.29</v>
+      </c>
+      <c r="K629" t="n">
+        <v>319.49</v>
+      </c>
+      <c r="L629" t="n">
+        <v>328.63</v>
+      </c>
+      <c r="M629" t="n">
+        <v>340.95</v>
+      </c>
+      <c r="N629" t="n">
+        <v>300.15</v>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>330.2</v>
+      </c>
+      <c r="C630" t="n">
+        <v>312.79</v>
+      </c>
+      <c r="D630" t="n">
+        <v>312.8</v>
+      </c>
+      <c r="E630" t="n">
+        <v>310.34</v>
+      </c>
+      <c r="F630" t="n">
+        <v>311.1</v>
+      </c>
+      <c r="G630" t="n">
+        <v>315.48</v>
+      </c>
+      <c r="H630" t="n">
+        <v>315.38</v>
+      </c>
+      <c r="I630" t="n">
+        <v>311.41</v>
+      </c>
+      <c r="J630" t="n">
+        <v>313.22</v>
+      </c>
+      <c r="K630" t="n">
+        <v>320.03</v>
+      </c>
+      <c r="L630" t="n">
+        <v>328.65</v>
+      </c>
+      <c r="M630" t="n">
+        <v>340.49</v>
+      </c>
+      <c r="N630" t="n">
+        <v>296.74</v>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -32419,7 +32572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B704"/>
+  <dimension ref="A1:B707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39462,6 +39615,36 @@
       </c>
       <c r="B704" t="n">
         <v>0.4</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -39630,28 +39813,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2567371191755962</v>
+        <v>0.2619102801737954</v>
       </c>
       <c r="J2" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K2" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02301903648843495</v>
+        <v>0.02414164577863254</v>
       </c>
       <c r="M2" t="n">
-        <v>8.782387660259527</v>
+        <v>8.761788554798246</v>
       </c>
       <c r="N2" t="n">
-        <v>121.830499647129</v>
+        <v>121.3750954649203</v>
       </c>
       <c r="O2" t="n">
-        <v>11.03768542979592</v>
+        <v>11.0170366008705</v>
       </c>
       <c r="P2" t="n">
-        <v>318.8567568604093</v>
+        <v>318.79243958113</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -39712,28 +39895,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04525996710224812</v>
+        <v>-0.04016612768273164</v>
       </c>
       <c r="J3" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K3" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005150673858044907</v>
+        <v>0.004073930431946704</v>
       </c>
       <c r="M3" t="n">
-        <v>3.371527830027529</v>
+        <v>3.373318103430558</v>
       </c>
       <c r="N3" t="n">
-        <v>17.230642211978</v>
+        <v>17.26386392949499</v>
       </c>
       <c r="O3" t="n">
-        <v>4.150980873477738</v>
+        <v>4.154980617222539</v>
       </c>
       <c r="P3" t="n">
-        <v>309.3681741691522</v>
+        <v>309.3048346100286</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39790,28 +39973,28 @@
         <v>0.1631</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1615094092385318</v>
+        <v>-0.1575194680968326</v>
       </c>
       <c r="J4" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K4" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08700044717369904</v>
+        <v>0.08340161680418778</v>
       </c>
       <c r="M4" t="n">
-        <v>2.734013497792208</v>
+        <v>2.738892914841824</v>
       </c>
       <c r="N4" t="n">
-        <v>11.92132354302994</v>
+        <v>11.93651844416047</v>
       </c>
       <c r="O4" t="n">
-        <v>3.452726971978807</v>
+        <v>3.454926691575448</v>
       </c>
       <c r="P4" t="n">
-        <v>313.5673429396172</v>
+        <v>313.5177328280175</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39868,28 +40051,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1908010758764516</v>
+        <v>-0.1884878729256238</v>
       </c>
       <c r="J5" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K5" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09504801975597577</v>
+        <v>0.09365623065387385</v>
       </c>
       <c r="M5" t="n">
-        <v>3.113637058334417</v>
+        <v>3.109204826415265</v>
       </c>
       <c r="N5" t="n">
-        <v>15.09933130731916</v>
+        <v>15.05390588483741</v>
       </c>
       <c r="O5" t="n">
-        <v>3.885785803067271</v>
+        <v>3.879936324843155</v>
       </c>
       <c r="P5" t="n">
-        <v>313.3217956611426</v>
+        <v>313.2930170809175</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39946,28 +40129,28 @@
         <v>0.142</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1813867971877424</v>
+        <v>-0.1779067763744235</v>
       </c>
       <c r="J6" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K6" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06877830295211618</v>
+        <v>0.06676973986029011</v>
       </c>
       <c r="M6" t="n">
-        <v>3.489769910129285</v>
+        <v>3.487170089618465</v>
       </c>
       <c r="N6" t="n">
-        <v>19.40557830524416</v>
+        <v>19.36957983424025</v>
       </c>
       <c r="O6" t="n">
-        <v>4.405176308077142</v>
+        <v>4.401088482891505</v>
       </c>
       <c r="P6" t="n">
-        <v>313.2370585747129</v>
+        <v>313.1937618154346</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -40024,28 +40207,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1717920446679935</v>
+        <v>-0.1678976776812779</v>
       </c>
       <c r="J7" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K7" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06956437887943001</v>
+        <v>0.06701310020365958</v>
       </c>
       <c r="M7" t="n">
-        <v>3.302592447902974</v>
+        <v>3.302287340400031</v>
       </c>
       <c r="N7" t="n">
-        <v>17.19037109127717</v>
+        <v>17.17947141781103</v>
       </c>
       <c r="O7" t="n">
-        <v>4.146127240121457</v>
+        <v>4.144812591397955</v>
       </c>
       <c r="P7" t="n">
-        <v>317.2495147309755</v>
+        <v>317.2010982251651</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -40102,28 +40285,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2010251747334287</v>
+        <v>-0.1982444889236984</v>
       </c>
       <c r="J8" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K8" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1338343142443176</v>
+        <v>0.1313793958555775</v>
       </c>
       <c r="M8" t="n">
-        <v>2.745922123218074</v>
+        <v>2.745514959451513</v>
       </c>
       <c r="N8" t="n">
-        <v>11.38974840693596</v>
+        <v>11.37390759659915</v>
       </c>
       <c r="O8" t="n">
-        <v>3.374870131862255</v>
+        <v>3.372522438264741</v>
       </c>
       <c r="P8" t="n">
-        <v>318.9745590373367</v>
+        <v>318.939992239404</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40180,28 +40363,28 @@
         <v>0.0941</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1814819818132174</v>
+        <v>-0.1821544655541209</v>
       </c>
       <c r="J9" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K9" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09599380413707437</v>
+        <v>0.0974790732723303</v>
       </c>
       <c r="M9" t="n">
-        <v>2.912092594449589</v>
+        <v>2.902781719035655</v>
       </c>
       <c r="N9" t="n">
-        <v>13.5074997578192</v>
+        <v>13.44714590740098</v>
       </c>
       <c r="O9" t="n">
-        <v>3.675255060239929</v>
+        <v>3.667035029475582</v>
       </c>
       <c r="P9" t="n">
-        <v>317.2701643455036</v>
+        <v>317.2785357573375</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40258,28 +40441,28 @@
         <v>0.0854</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2218043047922216</v>
+        <v>-0.2221403429625407</v>
       </c>
       <c r="J10" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K10" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09182709304517722</v>
+        <v>0.09289239490838286</v>
       </c>
       <c r="M10" t="n">
-        <v>3.629977688973034</v>
+        <v>3.617357617683225</v>
       </c>
       <c r="N10" t="n">
-        <v>21.18933780397804</v>
+        <v>21.09298809318677</v>
       </c>
       <c r="O10" t="n">
-        <v>4.603187787172932</v>
+        <v>4.592710321061712</v>
       </c>
       <c r="P10" t="n">
-        <v>320.1322541093612</v>
+        <v>320.1364456471509</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40336,28 +40519,28 @@
         <v>0.1648</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2458099716688016</v>
+        <v>-0.2462297781508837</v>
       </c>
       <c r="J11" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K11" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07846702171884545</v>
+        <v>0.07938059423940536</v>
       </c>
       <c r="M11" t="n">
-        <v>4.36453292598211</v>
+        <v>4.35415390877062</v>
       </c>
       <c r="N11" t="n">
-        <v>30.90312822468079</v>
+        <v>30.77878771378748</v>
       </c>
       <c r="O11" t="n">
-        <v>5.559058213823704</v>
+        <v>5.54786334671173</v>
       </c>
       <c r="P11" t="n">
-        <v>328.2081876287031</v>
+        <v>328.2134359901058</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40414,28 +40597,28 @@
         <v>0.0694</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2065639923284184</v>
+        <v>-0.2086004961980414</v>
       </c>
       <c r="J12" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K12" t="n">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03423321219668674</v>
+        <v>0.03521127446861139</v>
       </c>
       <c r="M12" t="n">
-        <v>5.461653280879354</v>
+        <v>5.446151173032677</v>
       </c>
       <c r="N12" t="n">
-        <v>52.17662907442385</v>
+        <v>51.94610088615916</v>
       </c>
       <c r="O12" t="n">
-        <v>7.223339191428287</v>
+        <v>7.20736435086774</v>
       </c>
       <c r="P12" t="n">
-        <v>336.3414263925181</v>
+        <v>336.3668225431628</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -40496,28 +40679,28 @@
         <v>0.0512</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06365303514054675</v>
+        <v>0.06295585961632616</v>
       </c>
       <c r="J13" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K13" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001666994455887472</v>
+        <v>0.00164691508174708</v>
       </c>
       <c r="M13" t="n">
-        <v>7.430210796682655</v>
+        <v>7.398439729697298</v>
       </c>
       <c r="N13" t="n">
-        <v>105.2829929730919</v>
+        <v>104.7820824818715</v>
       </c>
       <c r="O13" t="n">
-        <v>10.26075011746665</v>
+        <v>10.23631195704153</v>
       </c>
       <c r="P13" t="n">
-        <v>339.9352972569205</v>
+        <v>339.9439941272082</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -40578,28 +40761,28 @@
         <v>0.0428</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5191138203111521</v>
+        <v>0.490944056893893</v>
       </c>
       <c r="J14" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K14" t="n">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02751692996909572</v>
+        <v>0.02472103255779068</v>
       </c>
       <c r="M14" t="n">
-        <v>13.48491190593647</v>
+        <v>13.51625171895288</v>
       </c>
       <c r="N14" t="n">
-        <v>402.5365207888181</v>
+        <v>404.0061438863031</v>
       </c>
       <c r="O14" t="n">
-        <v>20.06331280693241</v>
+        <v>20.09990407654482</v>
       </c>
       <c r="P14" t="n">
-        <v>313.682895035882</v>
+        <v>314.0388739213103</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -40641,7 +40824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O627"/>
+  <dimension ref="A1:O630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88871,6 +89054,237 @@
         </is>
       </c>
     </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>-45.18302426021993,170.90582373601526</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>-45.182940805128,170.90487005345028</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>-45.18318894836884,170.90395515811176</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>-45.18355819997428,170.9031469601335</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>-45.1840252071821,170.90248388593133</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>-45.18453415285627,170.90190392151752</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>-45.18506184587794,170.90135492425125</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>-45.18560438446664,170.90084230626562</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>-45.18618640823489,170.90046069402078</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>-45.186785966845626,170.9001739587109</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>-45.18734570022503,170.89976615334854</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>-45.18794628277467,170.89943817652505</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>-45.1885473650919,170.89894588953823</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>-45.1829973253948,170.90581969635127</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>-45.18293089574883,170.90486682843516</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>-45.1831770681679,170.90394664698562</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>-45.183544176819005,170.9031312127634</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>-45.18401427172282,170.9024685779265</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>-45.184524888984214,170.901888502838</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>-45.18505330143272,170.9013369811143</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>-45.18559787128012,170.90082587936317</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>-45.186178245950785,170.90043844124583</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>-45.18676436582182,170.90012033171192</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>-45.18734192896919,170.8997576316443</t>
+        </is>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>-45.18794495497408,170.89943236414493</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>-45.188543909222396,170.89887288160864</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>-45.18300439466786,170.905820756595</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>-45.18293186037866,170.90486714237466</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>-45.183178914415386,170.90394796966038</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>-45.183549532396135,170.90313722683348</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>-45.18401312062173,170.9024669665579</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>-45.184520927076065,170.90188190868727</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>-45.18505038626842,170.90133085933942</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>-45.18559853140047,170.90082754425174</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>-45.186177955920314,170.90043765053818</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>-45.1867667708855,170.900126302551</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>-45.18734202444402,170.89975784738365</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>-45.18794368249826,170.89942679394755</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>-45.18854185971954,170.8988295847371</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0476/nzd0476.xlsx
+++ b/data/nzd0476/nzd0476.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O630"/>
+  <dimension ref="A1:O632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32553,9 +32553,111 @@
         <v>340.49</v>
       </c>
       <c r="N630" t="n">
-        <v>296.74</v>
+        <v>299.61</v>
       </c>
       <c r="O630" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="C631" t="n">
+        <v>311.92</v>
+      </c>
+      <c r="D631" t="n">
+        <v>312.07</v>
+      </c>
+      <c r="E631" t="n">
+        <v>309.91</v>
+      </c>
+      <c r="F631" t="n">
+        <v>310.58</v>
+      </c>
+      <c r="G631" t="n">
+        <v>314.59</v>
+      </c>
+      <c r="H631" t="n">
+        <v>314.88</v>
+      </c>
+      <c r="I631" t="n">
+        <v>311.15</v>
+      </c>
+      <c r="J631" t="n">
+        <v>312.77</v>
+      </c>
+      <c r="K631" t="n">
+        <v>319.73</v>
+      </c>
+      <c r="L631" t="n">
+        <v>329.04</v>
+      </c>
+      <c r="M631" t="n">
+        <v>340.62</v>
+      </c>
+      <c r="N631" t="n">
+        <v>299.23</v>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:09+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="C632" t="n">
+        <v>311.92</v>
+      </c>
+      <c r="D632" t="n">
+        <v>313.63</v>
+      </c>
+      <c r="E632" t="n">
+        <v>311.07</v>
+      </c>
+      <c r="F632" t="n">
+        <v>310.14</v>
+      </c>
+      <c r="G632" t="n">
+        <v>313.9</v>
+      </c>
+      <c r="H632" t="n">
+        <v>314.88</v>
+      </c>
+      <c r="I632" t="n">
+        <v>311.25</v>
+      </c>
+      <c r="J632" t="n">
+        <v>312.77</v>
+      </c>
+      <c r="K632" t="n">
+        <v>319.73</v>
+      </c>
+      <c r="L632" t="n">
+        <v>328.79</v>
+      </c>
+      <c r="M632" t="n">
+        <v>340.54</v>
+      </c>
+      <c r="N632" t="n">
+        <v>297.25</v>
+      </c>
+      <c r="O632" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32572,7 +32674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B707"/>
+  <dimension ref="A1:B709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39645,6 +39747,26 @@
       </c>
       <c r="B707" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
@@ -39813,28 +39935,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2619102801737954</v>
+        <v>0.2629691356808489</v>
       </c>
       <c r="J2" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K2" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02414164577863254</v>
+        <v>0.0244892202432706</v>
       </c>
       <c r="M2" t="n">
-        <v>8.761788554798246</v>
+        <v>8.738304825538995</v>
       </c>
       <c r="N2" t="n">
-        <v>121.3750954649203</v>
+        <v>120.9977776750094</v>
       </c>
       <c r="O2" t="n">
-        <v>11.0170366008705</v>
+        <v>10.99989898476388</v>
       </c>
       <c r="P2" t="n">
-        <v>318.79243958113</v>
+        <v>318.7792177100769</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -39895,28 +40017,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04016612768273164</v>
+        <v>-0.03762481152076327</v>
       </c>
       <c r="J3" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K3" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004073930431946704</v>
+        <v>0.003591407789039991</v>
       </c>
       <c r="M3" t="n">
-        <v>3.373318103430558</v>
+        <v>3.371418062116478</v>
       </c>
       <c r="N3" t="n">
-        <v>17.26386392949499</v>
+        <v>17.25170923744005</v>
       </c>
       <c r="O3" t="n">
-        <v>4.154980617222539</v>
+        <v>4.153517694369442</v>
       </c>
       <c r="P3" t="n">
-        <v>309.3048346100286</v>
+        <v>309.2731013131574</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39973,28 +40095,28 @@
         <v>0.1631</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1575194680968326</v>
+        <v>-0.1550853296780246</v>
       </c>
       <c r="J4" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K4" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08340161680418778</v>
+        <v>0.08129030071881538</v>
       </c>
       <c r="M4" t="n">
-        <v>2.738892914841824</v>
+        <v>2.741028306956214</v>
       </c>
       <c r="N4" t="n">
-        <v>11.93651844416047</v>
+        <v>11.93965359111844</v>
       </c>
       <c r="O4" t="n">
-        <v>3.454926691575448</v>
+        <v>3.455380382985127</v>
       </c>
       <c r="P4" t="n">
-        <v>313.5177328280175</v>
+        <v>313.4873353734753</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -40051,28 +40173,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1884878729256238</v>
+        <v>-0.1869554862650487</v>
       </c>
       <c r="J5" t="n">
+        <v>631</v>
+      </c>
+      <c r="K5" t="n">
         <v>629</v>
       </c>
-      <c r="K5" t="n">
-        <v>627</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.09365623065387385</v>
+        <v>0.09274387703311315</v>
       </c>
       <c r="M5" t="n">
-        <v>3.109204826415265</v>
+        <v>3.106149152520285</v>
       </c>
       <c r="N5" t="n">
-        <v>15.05390588483741</v>
+        <v>15.02260253820698</v>
       </c>
       <c r="O5" t="n">
-        <v>3.879936324843155</v>
+        <v>3.875900222942662</v>
       </c>
       <c r="P5" t="n">
-        <v>313.2930170809175</v>
+        <v>313.2738662071267</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -40129,28 +40251,28 @@
         <v>0.142</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1779067763744235</v>
+        <v>-0.176590838330745</v>
       </c>
       <c r="J6" t="n">
+        <v>631</v>
+      </c>
+      <c r="K6" t="n">
         <v>629</v>
       </c>
-      <c r="K6" t="n">
-        <v>627</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.06676973986029011</v>
+        <v>0.06622257932345443</v>
       </c>
       <c r="M6" t="n">
-        <v>3.487170089618465</v>
+        <v>3.481347036460862</v>
       </c>
       <c r="N6" t="n">
-        <v>19.36957983424025</v>
+        <v>19.31958087157548</v>
       </c>
       <c r="O6" t="n">
-        <v>4.401088482891505</v>
+        <v>4.395404517399449</v>
       </c>
       <c r="P6" t="n">
-        <v>313.1937618154346</v>
+        <v>313.1773182880226</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -40207,28 +40329,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1678976776812779</v>
+        <v>-0.1668514866798962</v>
       </c>
       <c r="J7" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K7" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06701310020365958</v>
+        <v>0.06662019152501275</v>
       </c>
       <c r="M7" t="n">
-        <v>3.302287340400031</v>
+        <v>3.295945975442142</v>
       </c>
       <c r="N7" t="n">
-        <v>17.17947141781103</v>
+        <v>17.13260516183103</v>
       </c>
       <c r="O7" t="n">
-        <v>4.144812591397955</v>
+        <v>4.139155126572454</v>
       </c>
       <c r="P7" t="n">
-        <v>317.2010982251651</v>
+        <v>317.1880355700627</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -40285,28 +40407,28 @@
         <v>0.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1982444889236984</v>
+        <v>-0.1973983848249685</v>
       </c>
       <c r="J8" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K8" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1313793958555775</v>
+        <v>0.131113991743887</v>
       </c>
       <c r="M8" t="n">
-        <v>2.745514959451513</v>
+        <v>2.740608799777401</v>
       </c>
       <c r="N8" t="n">
-        <v>11.37390759659915</v>
+        <v>11.34257537460499</v>
       </c>
       <c r="O8" t="n">
-        <v>3.372522438264741</v>
+        <v>3.367874014063618</v>
       </c>
       <c r="P8" t="n">
-        <v>318.939992239404</v>
+        <v>318.9294269711983</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40363,28 +40485,28 @@
         <v>0.0941</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1821544655541209</v>
+        <v>-0.1830000773193878</v>
       </c>
       <c r="J9" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K9" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0974790732723303</v>
+        <v>0.09885602089176948</v>
       </c>
       <c r="M9" t="n">
-        <v>2.902781719035655</v>
+        <v>2.898188036499254</v>
       </c>
       <c r="N9" t="n">
-        <v>13.44714590740098</v>
+        <v>13.40924502057235</v>
       </c>
       <c r="O9" t="n">
-        <v>3.667035029475582</v>
+        <v>3.66186359939476</v>
       </c>
       <c r="P9" t="n">
-        <v>317.2785357573375</v>
+        <v>317.2890947150621</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40441,28 +40563,28 @@
         <v>0.0854</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2221403429625407</v>
+        <v>-0.2231412254384464</v>
       </c>
       <c r="J10" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K10" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09289239490838286</v>
+        <v>0.09419135914362675</v>
       </c>
       <c r="M10" t="n">
-        <v>3.617357617683225</v>
+        <v>3.6103265376467</v>
       </c>
       <c r="N10" t="n">
-        <v>21.09298809318677</v>
+        <v>21.03273467749983</v>
       </c>
       <c r="O10" t="n">
-        <v>4.592710321061712</v>
+        <v>4.586145950305096</v>
       </c>
       <c r="P10" t="n">
-        <v>320.1364456471509</v>
+        <v>320.1489436128951</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40519,28 +40641,28 @@
         <v>0.1648</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2462297781508837</v>
+        <v>-0.2475562662445753</v>
       </c>
       <c r="J11" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K11" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07938059423940536</v>
+        <v>0.08063261459309234</v>
       </c>
       <c r="M11" t="n">
-        <v>4.35415390877062</v>
+        <v>4.346797872063789</v>
       </c>
       <c r="N11" t="n">
-        <v>30.77878771378748</v>
+        <v>30.69282890473915</v>
       </c>
       <c r="O11" t="n">
-        <v>5.54786334671173</v>
+        <v>5.540110910869849</v>
       </c>
       <c r="P11" t="n">
-        <v>328.2134359901058</v>
+        <v>328.2299997771854</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40597,28 +40719,28 @@
         <v>0.0694</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2086004961980414</v>
+        <v>-0.2099119738208411</v>
       </c>
       <c r="J12" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K12" t="n">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03521127446861139</v>
+        <v>0.03586148313165527</v>
       </c>
       <c r="M12" t="n">
-        <v>5.446151173032677</v>
+        <v>5.435587359642678</v>
       </c>
       <c r="N12" t="n">
-        <v>51.94610088615916</v>
+        <v>51.79249807893088</v>
       </c>
       <c r="O12" t="n">
-        <v>7.20736435086774</v>
+        <v>7.196700499460214</v>
       </c>
       <c r="P12" t="n">
-        <v>336.3668225431628</v>
+        <v>336.3832416167638</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -40679,28 +40801,28 @@
         <v>0.0512</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06295585961632616</v>
+        <v>0.06223368410261142</v>
       </c>
       <c r="J13" t="n">
+        <v>631</v>
+      </c>
+      <c r="K13" t="n">
         <v>629</v>
       </c>
-      <c r="K13" t="n">
-        <v>627</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.00164691508174708</v>
+        <v>0.001620076496545275</v>
       </c>
       <c r="M13" t="n">
-        <v>7.398439729697298</v>
+        <v>7.37878191336759</v>
       </c>
       <c r="N13" t="n">
-        <v>104.7820824818715</v>
+        <v>104.4523369890063</v>
       </c>
       <c r="O13" t="n">
-        <v>10.23631195704153</v>
+        <v>10.22019261017161</v>
       </c>
       <c r="P13" t="n">
-        <v>339.9439941272082</v>
+        <v>339.9530345235469</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -40761,28 +40883,28 @@
         <v>0.0428</v>
       </c>
       <c r="I14" t="n">
-        <v>0.490944056893893</v>
+        <v>0.4714887547251777</v>
       </c>
       <c r="J14" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K14" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02472103255779068</v>
+        <v>0.02286307465620041</v>
       </c>
       <c r="M14" t="n">
-        <v>13.51625171895288</v>
+        <v>13.54024795787549</v>
       </c>
       <c r="N14" t="n">
-        <v>404.0061438863031</v>
+        <v>405.0958782581476</v>
       </c>
       <c r="O14" t="n">
-        <v>20.09990407654482</v>
+        <v>20.12699377100683</v>
       </c>
       <c r="P14" t="n">
-        <v>314.0388739213103</v>
+        <v>314.2857238389504</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -40824,7 +40946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O630"/>
+  <dimension ref="A1:O632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89276,10 +89398,164 @@
       </c>
       <c r="N630" t="inlineStr">
         <is>
-          <t>-45.18854185971954,170.8988295847371</t>
+          <t>-45.188543584668786,170.8988660252123</t>
         </is>
       </c>
       <c r="O630" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>-45.182978444171766,170.9058168645622</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>-45.18292423103358,170.90486465939904</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>-45.18317305458636,170.90394377160595</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>-45.18354650226701,170.9031338241358</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>-45.18400979521845,170.90246231149348</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>-45.1845157416369,170.9018732781091</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>-45.18504787319551,170.9013255819478</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>-45.185597387191834,170.9008246584449</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>-45.18617609143855,170.90043256741797</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>-45.18676543473905,170.90012298541814</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>-45.18734388620331,170.89976205430077</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>-45.187944042111006,170.89942836813375</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>-45.18854335627896,170.8988612003409</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:09+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>-45.182978444171766,170.9058168645622</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>-45.18292423103358,170.90486465939904</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>-45.18318557696053,170.9039527427918</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>-45.18355467656863,170.90314300350713</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>-45.18400698141554,170.9024583725932</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>-45.184511721464524,170.9018665869877</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>-45.18504787319551,170.9013255819478</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>-45.18559782727209,170.9008257683706</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>-45.18617609143855,170.90043256741797</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>-45.18676543473905,170.90012298541814</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>-45.18734269276789,170.899759357559</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>-45.18794382081085,170.89942739940378</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>-45.188542166244474,170.89883606022207</t>
+        </is>
+      </c>
+      <c r="O632" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
